--- a/mapping/Plastid.xlsx
+++ b/mapping/Plastid.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,7 +964,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>微虎耳草属</t>
+          <t>虎耳草属</t>
         </is>
       </c>
     </row>
@@ -1199,22 +1199,58 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Megathyrsus</t>
+          <t>Nicotiana</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>大黍属</t>
+          <t>烟草属</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Idesia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>山桐子属</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Steudnera</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>泉七属</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Megathyrsus</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>大黍属</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Binuclearia</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>双核藻属</t>
         </is>
